--- a/events/Rio_2016_PG/Rio_2016_PG_Results.xlsx
+++ b/events/Rio_2016_PG/Rio_2016_PG_Results.xlsx
@@ -602,6 +602,11 @@
           <t>58.662</t>
         </is>
       </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>61471</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -737,6 +742,11 @@
           <t>+4.996</t>
         </is>
       </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>69298</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2296,6 +2306,11 @@
           <t>57.145</t>
         </is>
       </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>46444</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3051,6 +3066,11 @@
           <t>+1.445</t>
         </is>
       </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>61146</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -4146,6 +4166,11 @@
           <t>+2.023</t>
         </is>
       </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>35799</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -4761,6 +4786,11 @@
           <t>+0.429</t>
         </is>
       </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>69298</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -6670,6 +6700,11 @@
           <t>42.852</t>
         </is>
       </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>35799</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -7154,6 +7189,11 @@
           <t>+0.114</t>
         </is>
       </c>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>61471</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -7365,6 +7405,11 @@
           <t>+4.601</t>
         </is>
       </c>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>69298</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -8281,6 +8326,11 @@
           <t>+2.311</t>
         </is>
       </c>
+      <c r="R114" t="inlineStr">
+        <is>
+          <t>46444</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -8919,6 +8969,11 @@
           <t>+2.746</t>
         </is>
       </c>
+      <c r="R123" t="inlineStr">
+        <is>
+          <t>61146</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -10193,6 +10248,11 @@
       <c r="Q141" t="inlineStr">
         <is>
           <t>+2.600</t>
+        </is>
+      </c>
+      <c r="R141" t="inlineStr">
+        <is>
+          <t>35799</t>
         </is>
       </c>
     </row>
@@ -10423,7 +10483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D53"/>
+  <dimension ref="A1:D58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11592,6 +11652,116 @@
         </is>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>61471</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Edina</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>MUELLER</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>69298</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Jocelyn</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>NEUMUELLER</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>46444</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Nataliia</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>LAHUTENKO</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>35799</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Robert</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>OLIVER</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>61146</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Nicholas</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>BEIGHTON</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
